--- a/data/catches.xlsx
+++ b/data/catches.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="536" uniqueCount="181">
   <si>
     <t>id</t>
   </si>
@@ -31,6 +31,9 @@
     <t>longitude</t>
   </si>
   <si>
+    <t>water_body</t>
+  </si>
+  <si>
     <t>date_caught</t>
   </si>
   <si>
@@ -64,7 +67,7 @@
     <t>First time I've ever caught one of these.  The bass must feast on them.</t>
   </si>
   <si>
-    <t>https://photos.fife.usercontent.google.com/pw/AP1GczOHw6-7mk5Iac72wGM_NCApv-frRaRUl6hyDjrrncZTdpRJoSdpfeksUA=w708-h944-s-no-gm?authuser=0</t>
+    <t>IMG_20210418_144536.jpg</t>
   </si>
   <si>
     <t>Largemouth Bass</t>
@@ -79,7 +82,7 @@
     <t>Excellent spot to slam largemouth</t>
   </si>
   <si>
-    <t>https://photos.fife.usercontent.google.com/pw/AP1GczOZY8vZXoqqV5YSbDHGv6esLwsSaacT1UqEMVIRnDSo0J_W8Ey8NigwyQ=w708-h944-s-no-gm?authuser=0</t>
+    <t>IMG_20210418_152824.jpg</t>
   </si>
   <si>
     <t>Rainbow Trout</t>
@@ -94,7 +97,7 @@
     <t>One of the first stocked trout I've ever caught.</t>
   </si>
   <si>
-    <t>https://photos.fife.usercontent.google.com/pw/AP1GczMnmQ8hJOvOMfI2EegdmygCTkQ74SaKWHu6-kBQfdK1K2VTpsLUoT4vIw=w918-h516-s-no-gm?authuser=0</t>
+    <t>rainbow-1.jpg</t>
   </si>
   <si>
     <t>1lb</t>
@@ -106,19 +109,19 @@
     <t>Sunny, Warm</t>
   </si>
   <si>
-    <t>https://photos.fife.usercontent.google.com/pw/AP1GczOhE1575OYuac1M2SpmwXwxBzVZr6joAqCFVp-dwZ6VK6n4QJ4kGJqBGg=w708-h944-s-no-gm?authuser=0</t>
+    <t>IMG_20210427_161111.jpg</t>
   </si>
   <si>
     <t>Sunny, Cool</t>
   </si>
   <si>
-    <t>https://photos.fife.usercontent.google.com/pw/AP1GczMGA3soUHmM412dR3Amw_i-_WF50EMsOiU9DQp4KOYCNByvxg1Ag2DbFQ=w708-h944-s-no-gm?authuser=0</t>
+    <t>IMG_20210504_161039.jpg</t>
   </si>
   <si>
     <t>1lb 11oz</t>
   </si>
   <si>
-    <t>https://photos.fife.usercontent.google.com/pw/AP1GczNZ2MnwbdTb2lX1XONDfZvFqcyDbB02rYmxnGd5Z6U9uiCUKJsw1hQxtg=w708-h944-s-no-gm?authuser=0</t>
+    <t>IMG_20210505_171019.jpg</t>
   </si>
   <si>
     <t>2lb</t>
@@ -127,13 +130,13 @@
     <t>Warm, Foggy</t>
   </si>
   <si>
-    <t>https://photos.fife.usercontent.google.com/pw/AP1GczMlE5PWZYRbw3SxdVPvTNpdeifG17lbb2Cgvi8gR6H-mJF-ezxfZRsAAg=w918-h516-s-no-gm?authuser=0</t>
+    <t>lmb-latest.jpg</t>
   </si>
   <si>
     <t>Warm, Sunny</t>
   </si>
   <si>
-    <t>https://photos.fife.usercontent.google.com/pw/AP1GczPSNQTGKruRkOlSNtt1dxir1BKntAakfoAZnsFjhXF5iRZv2zGqXcjyYQ=w708-h944-s-no-gm?authuser=0</t>
+    <t>IMG_20210615_183205.jpg</t>
   </si>
   <si>
     <t>Yellow Bullhead Catfish</t>
@@ -142,25 +145,429 @@
     <t>Chicken</t>
   </si>
   <si>
-    <t>https://photos.fife.usercontent.google.com/pw/AP1GczNziMXAucm4sZzqv76TUfvC3FyubkOuTSDmSQoTXubJ0Q3ajQg_Am_Ttg=w918-h689-s-no-gm?authuser=0</t>
+    <t>IMG_20210616_180157.jpg</t>
   </si>
   <si>
     <t>3lb</t>
   </si>
   <si>
-    <t>https://photos.fife.usercontent.google.com/pw/AP1GczNjeeitRod1deFwf1S5mblLMA_KHKcPMzJJBPJLSZoSJm_qUtH-xz0YNA=w708-h944-s-no-gm?authuser=0</t>
+    <t>IMG_20210621_165119.jpg</t>
+  </si>
+  <si>
+    <t>Best Lake</t>
+  </si>
+  <si>
+    <t>Cool, Cloudy</t>
+  </si>
+  <si>
+    <t>IMG_20211026_172751.jpg</t>
+  </si>
+  <si>
+    <t>IMG_20211027_174820.jpg</t>
+  </si>
+  <si>
+    <t>1lb 7oz</t>
+  </si>
+  <si>
+    <t>Bee Meadow</t>
+  </si>
+  <si>
+    <t>Cool, Sunny</t>
+  </si>
+  <si>
+    <t>IMG_20211031_174609_Bokeh.jpg</t>
+  </si>
+  <si>
+    <t>Common Carp</t>
+  </si>
+  <si>
+    <t>The Falls</t>
+  </si>
+  <si>
+    <t>Cold, Cloudy</t>
+  </si>
+  <si>
+    <t>IMG_20211101_172424.jpg</t>
+  </si>
+  <si>
+    <t>3lb 4oz</t>
+  </si>
+  <si>
+    <t>Lake Parsippany</t>
+  </si>
+  <si>
+    <t>IMG_20211117_150906.jpg</t>
+  </si>
+  <si>
+    <t>Yellow Perch</t>
+  </si>
+  <si>
+    <t>Little Falls Township</t>
+  </si>
+  <si>
+    <t>IMG_20211202_132927.jpg</t>
+  </si>
+  <si>
+    <t>IMG_20211205_123146.jpg</t>
+  </si>
+  <si>
+    <t>IMG_20211205_142440.jpg</t>
+  </si>
+  <si>
+    <t>Smallmouth Bass</t>
+  </si>
+  <si>
+    <t>2lb 10oz</t>
+  </si>
+  <si>
+    <t>Live Shiner</t>
+  </si>
+  <si>
+    <t>IMG_20220320_154046.jpg</t>
+  </si>
+  <si>
+    <t>Chain Pickeral</t>
+  </si>
+  <si>
+    <t>Cold, Sunny</t>
+  </si>
+  <si>
+    <t>IMG_20220321_164912~2.jpg</t>
+  </si>
+  <si>
+    <t>Crappie Magnet</t>
+  </si>
+  <si>
+    <t>IMG_20220410_164537~2.jpg</t>
+  </si>
+  <si>
+    <t>3lb 5oz</t>
+  </si>
+  <si>
+    <t>IMG_20220411_135829~2.jpg</t>
+  </si>
+  <si>
+    <t>South Mountain Fairy Trail</t>
+  </si>
+  <si>
+    <t>Rooster Tail</t>
+  </si>
+  <si>
+    <t>IMG_20220413_141659.jpg</t>
+  </si>
+  <si>
+    <t>Dundee Dam</t>
+  </si>
+  <si>
+    <t>PXL_20220515_211503173.jpg</t>
+  </si>
+  <si>
+    <t>White Catfish</t>
+  </si>
+  <si>
+    <t>Sunny, Hot</t>
+  </si>
+  <si>
+    <t>IMG_4526.jpg</t>
+  </si>
+  <si>
+    <t>Channel Catfish</t>
+  </si>
+  <si>
+    <t>PXL_20220522_000852431.jpg</t>
+  </si>
+  <si>
+    <t>Grass Carp</t>
+  </si>
+  <si>
+    <t>Pearl River</t>
+  </si>
+  <si>
+    <t>Corn</t>
+  </si>
+  <si>
+    <t>Sweltering Hot</t>
+  </si>
+  <si>
+    <t>PXL_20220603_233639334.jpg</t>
+  </si>
+  <si>
+    <t>Pompton Lakes</t>
+  </si>
+  <si>
+    <t>Crankbait</t>
+  </si>
+  <si>
+    <t>Warm, Cloudy</t>
+  </si>
+  <si>
+    <t>PXL_20220607_201655387.jpg</t>
+  </si>
+  <si>
+    <t>Striped Bass</t>
+  </si>
+  <si>
+    <t>Passiac River</t>
+  </si>
+  <si>
+    <t>Blood Worm</t>
+  </si>
+  <si>
+    <t>Hot, Sunny</t>
+  </si>
+  <si>
+    <t>PXL_20220612_221124337.jpg</t>
+  </si>
+  <si>
+    <t>PXL_20220813_213944604.jpg</t>
+  </si>
+  <si>
+    <t>Shallcross</t>
+  </si>
+  <si>
+    <t>Crawdaddy</t>
+  </si>
+  <si>
+    <t>PXL_20220928_205846310.jpg</t>
+  </si>
+  <si>
+    <t>Keitech</t>
+  </si>
+  <si>
+    <t>Cold</t>
+  </si>
+  <si>
+    <t>PXL_20221221_015538970~2.jpg</t>
+  </si>
+  <si>
+    <t>PXL_20221230_212215226.PORTRAIT.jpg</t>
+  </si>
+  <si>
+    <t>PXL_20230103_222451685.PORTRAIT.jpg</t>
+  </si>
+  <si>
+    <t>Gizzard Shad</t>
+  </si>
+  <si>
+    <t>Swimbait (snagged)</t>
+  </si>
+  <si>
+    <t>Moderate</t>
+  </si>
+  <si>
+    <t>PXL_20230104_214520954.jpg</t>
+  </si>
+  <si>
+    <t>Swimbait</t>
+  </si>
+  <si>
+    <t>PXL_20230111_030101335.jpg</t>
+  </si>
+  <si>
+    <t>Rockaway River</t>
+  </si>
+  <si>
+    <t>Cool</t>
+  </si>
+  <si>
+    <t>PXL_20230320_222615031.jpg</t>
+  </si>
+  <si>
+    <t>PXL_20230327_175045176.PORTRAIT.jpg</t>
+  </si>
+  <si>
+    <t>Warm</t>
+  </si>
+  <si>
+    <t>PXL_20230404_211818350.jpg</t>
+  </si>
+  <si>
+    <t>PXL_20230410_204036629.jpg</t>
+  </si>
+  <si>
+    <t>Baby Whale</t>
+  </si>
+  <si>
+    <t>Cloudy</t>
+  </si>
+  <si>
+    <t>PXL_20230423_183441169.jpg</t>
+  </si>
+  <si>
+    <t>Black Crappie</t>
+  </si>
+  <si>
+    <t>Sunny</t>
+  </si>
+  <si>
+    <t>PXL_20230514_190449304~2.jpg</t>
+  </si>
+  <si>
+    <t>Rock Bass</t>
+  </si>
+  <si>
+    <t>The Falls (Behind)</t>
+  </si>
+  <si>
+    <t>PXL_20230604_224552859.jpg</t>
+  </si>
+  <si>
+    <t>Cranford</t>
+  </si>
+  <si>
+    <t>EFFECTS-lmb.jpg</t>
+  </si>
+  <si>
+    <t>PXL_20230719_201425207.jpg</t>
+  </si>
+  <si>
+    <t>PXL_20230704_190906250.jpg</t>
+  </si>
+  <si>
+    <t>Whippany River</t>
+  </si>
+  <si>
+    <t>PXL_20230704_220514882.jpg</t>
+  </si>
+  <si>
+    <t>PXL_20230704_221848501.jpg</t>
+  </si>
+  <si>
+    <t>PXL_20230804_215325097.jpg</t>
+  </si>
+  <si>
+    <t>PXL_20230806_190306695.jpg</t>
+  </si>
+  <si>
+    <t>PXL_20230808_194608502.jpg</t>
+  </si>
+  <si>
+    <t>Northern Pike</t>
+  </si>
+  <si>
+    <t>PXL_20230808_201913390.jpg</t>
+  </si>
+  <si>
+    <t>White Sucker</t>
+  </si>
+  <si>
+    <t>PXL_20230813_194408838.jpg</t>
+  </si>
+  <si>
+    <t>PXL_20230814_215501699.PORTRAIT.jpg</t>
+  </si>
+  <si>
+    <t>Willowbrook</t>
+  </si>
+  <si>
+    <t>PXL_20240130_194832132.jpg</t>
+  </si>
+  <si>
+    <t>IMG_0991jpg</t>
+  </si>
+  <si>
+    <t>PXL_20240130_204159133.jpg</t>
+  </si>
+  <si>
+    <t>Nomahegan Park</t>
+  </si>
+  <si>
+    <t>PXL_20240314_152038478.jpg</t>
+  </si>
+  <si>
+    <t>PXL_20240317_172747902~2.jpg</t>
+  </si>
+  <si>
+    <t>PXL_20240317_190530436.jpg</t>
+  </si>
+  <si>
+    <t>C-Lake</t>
+  </si>
+  <si>
+    <t>Mepps Spinner</t>
+  </si>
+  <si>
+    <t>PXL_20240401_133626850.jpg</t>
+  </si>
+  <si>
+    <t>PXL_20240409_183338141.jpg</t>
+  </si>
+  <si>
+    <t>Buzzbait</t>
+  </si>
+  <si>
+    <t>PXL_20240526_194450393.jpg</t>
+  </si>
+  <si>
+    <t>PXL_20240526_181457852.jpg</t>
+  </si>
+  <si>
+    <t>PXL_20240527_211336565.jpg</t>
+  </si>
+  <si>
+    <t>PXL_20240531_185333751.PORTRAIT.jpg</t>
+  </si>
+  <si>
+    <t>PXL_20240605_190207886.MP.jpg</t>
+  </si>
+  <si>
+    <t>PXL_20240605_201408813.MP.jpg</t>
+  </si>
+  <si>
+    <t>PXL_20240614_212147236.jpg</t>
+  </si>
+  <si>
+    <t>PXL_20240618_222359791.MP.jpg</t>
+  </si>
+  <si>
+    <t>PXL_20240624_000118562.jpg</t>
+  </si>
+  <si>
+    <t>Party Minnow</t>
+  </si>
+  <si>
+    <t>PXL_20240702_203726549.MP.jpg</t>
+  </si>
+  <si>
+    <t>PXL_20240704_174352545.jpg</t>
+  </si>
+  <si>
+    <t>PXL_20240704_203215958.MP.jpg</t>
+  </si>
+  <si>
+    <t>PXL_20240707_204304745.jpg</t>
+  </si>
+  <si>
+    <t>IMG-20240714-WA0006.jpg</t>
+  </si>
+  <si>
+    <t>Spruce Run</t>
+  </si>
+  <si>
+    <t>PXL_20240716_214419502.MP.jpg</t>
+  </si>
+  <si>
+    <t>20240909_165516.jpg</t>
+  </si>
+  <si>
+    <t>20240929_154203.jpg</t>
+  </si>
+  <si>
+    <t>20241118_130459.jpg</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <numFmts count="3">
+  <numFmts count="5">
     <numFmt numFmtId="164" formatCode="mmm d, yyyy"/>
     <numFmt numFmtId="165" formatCode="h:mm am/pm"/>
     <numFmt numFmtId="166" formatCode="mmmm d, yyyy"/>
+    <numFmt numFmtId="167" formatCode="mmm d,yyyy"/>
+    <numFmt numFmtId="168" formatCode="mmmm d yyyy"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -177,8 +584,12 @@
       <name val="&quot;Google Sans&quot;"/>
     </font>
     <font>
-      <u/>
-      <color rgb="FF0000FF"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <color rgb="FF5E5E5E"/>
+      <name val="Google Sans"/>
     </font>
   </fonts>
   <fills count="3">
@@ -201,7 +612,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="14">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -217,11 +628,32 @@
     <xf borderId="0" fillId="0" fontId="1" numFmtId="165" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="166" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="166" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="167" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="168" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="168" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="165" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -440,7 +872,9 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
-    <col customWidth="1" min="12" max="12" width="118.5"/>
+    <col customWidth="1" min="8" max="8" width="23.13"/>
+    <col customWidth="1" min="12" max="12" width="53.38"/>
+    <col customWidth="1" min="13" max="13" width="118.5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -483,10 +917,13 @@
       <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="2">
       <c r="B2" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C2" s="1">
         <v>5.0</v>
@@ -497,14 +934,12 @@
       <c r="F2" s="2">
         <v>-74.311383</v>
       </c>
-      <c r="G2" s="3">
+      <c r="G2" s="2"/>
+      <c r="H2" s="3">
         <v>44304.0</v>
       </c>
-      <c r="H2" s="4">
+      <c r="I2" s="4">
         <v>0.6145833333333334</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>14</v>
       </c>
       <c r="J2" s="1" t="s">
         <v>15</v>
@@ -512,19 +947,22 @@
       <c r="K2" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="L2" s="5" t="s">
+      <c r="L2" s="1" t="s">
         <v>17</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="3">
       <c r="B3" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C3" s="1">
         <v>14.0</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E3" s="2">
         <v>40.667818</v>
@@ -532,66 +970,68 @@
       <c r="F3" s="2">
         <v>-74.311455</v>
       </c>
-      <c r="G3" s="3">
+      <c r="G3" s="2"/>
+      <c r="H3" s="3">
         <v>44304.0</v>
       </c>
-      <c r="H3" s="4">
+      <c r="I3" s="4">
         <v>0.6444444444444445</v>
       </c>
-      <c r="I3" s="1" t="s">
-        <v>20</v>
-      </c>
       <c r="J3" s="1" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="L3" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="L3" s="1" t="s">
         <v>22</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="4">
       <c r="B4" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C4" s="1">
         <v>11.0</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="G4" s="3">
+        <v>25</v>
+      </c>
+      <c r="G4" s="1"/>
+      <c r="H4" s="3">
         <v>44311.0</v>
       </c>
-      <c r="H4" s="4">
+      <c r="I4" s="4">
         <v>0.7291666666666666</v>
       </c>
-      <c r="I4" s="1" t="s">
-        <v>25</v>
-      </c>
       <c r="J4" s="1" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="L4" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="L4" s="1" t="s">
         <v>27</v>
+      </c>
+      <c r="M4" s="1" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="5">
       <c r="B5" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C5" s="1">
         <v>12.0</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E5" s="2">
         <v>40.668859</v>
@@ -599,31 +1039,32 @@
       <c r="F5" s="2">
         <v>-74.313059</v>
       </c>
-      <c r="G5" s="3">
+      <c r="G5" s="2"/>
+      <c r="H5" s="3">
         <v>44313.0</v>
       </c>
-      <c r="H5" s="4">
+      <c r="I5" s="4">
         <v>0.6743055555555556</v>
-      </c>
-      <c r="I5" s="1" t="s">
-        <v>29</v>
       </c>
       <c r="J5" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="L5" s="5" t="s">
+      <c r="K5" s="1" t="s">
         <v>31</v>
+      </c>
+      <c r="M5" s="1" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="6">
       <c r="B6" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C6" s="1">
         <v>14.0</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E6" s="2">
         <v>40.628833</v>
@@ -631,31 +1072,32 @@
       <c r="F6" s="2">
         <v>-74.298279</v>
       </c>
-      <c r="G6" s="6">
+      <c r="G6" s="2"/>
+      <c r="H6" s="5">
         <v>44320.0</v>
       </c>
-      <c r="H6" s="4">
+      <c r="I6" s="4">
         <v>0.6736111111111112</v>
       </c>
-      <c r="I6" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="J6" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="L6" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="K6" s="1" t="s">
         <v>33</v>
+      </c>
+      <c r="M6" s="1" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="7">
       <c r="B7" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C7" s="1">
         <v>16.0</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E7" s="2">
         <v>40.66897</v>
@@ -663,31 +1105,32 @@
       <c r="F7" s="2">
         <v>-74.312867</v>
       </c>
-      <c r="G7" s="6">
+      <c r="G7" s="2"/>
+      <c r="H7" s="5">
         <v>44321.0</v>
       </c>
-      <c r="H7" s="4">
+      <c r="I7" s="4">
         <v>0.7152777777777778</v>
       </c>
-      <c r="I7" s="1" t="s">
-        <v>20</v>
-      </c>
       <c r="J7" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="L7" s="5" t="s">
-        <v>35</v>
+        <v>21</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="M7" s="1" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="8">
       <c r="B8" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C8" s="1">
         <v>15.0</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E8" s="2">
         <v>40.667818</v>
@@ -695,31 +1138,32 @@
       <c r="F8" s="2">
         <v>-74.311455</v>
       </c>
-      <c r="G8" s="6">
+      <c r="G8" s="2"/>
+      <c r="H8" s="5">
         <v>44361.0</v>
       </c>
-      <c r="H8" s="4">
+      <c r="I8" s="4">
         <v>0.5020833333333333</v>
       </c>
-      <c r="I8" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="J8" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="L8" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="K8" s="1" t="s">
         <v>38</v>
+      </c>
+      <c r="M8" s="1" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="9">
       <c r="B9" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C9" s="1">
         <v>12.0</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E9" s="2">
         <v>40.667794</v>
@@ -727,25 +1171,26 @@
       <c r="F9" s="2">
         <v>-74.311405</v>
       </c>
-      <c r="G9" s="6">
+      <c r="G9" s="2"/>
+      <c r="H9" s="5">
         <v>44362.0</v>
       </c>
-      <c r="H9" s="4">
+      <c r="I9" s="4">
         <v>0.7722222222222223</v>
       </c>
-      <c r="I9" s="1" t="s">
-        <v>20</v>
-      </c>
       <c r="J9" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="L9" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="K9" s="1" t="s">
         <v>40</v>
+      </c>
+      <c r="M9" s="1" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="10">
       <c r="B10" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E10" s="2">
         <v>40.659197</v>
@@ -753,28 +1198,29 @@
       <c r="F10" s="2">
         <v>-74.303087</v>
       </c>
-      <c r="G10" s="6">
+      <c r="G10" s="2"/>
+      <c r="H10" s="5">
         <v>44363.0</v>
       </c>
-      <c r="H10" s="4">
+      <c r="I10" s="4">
         <v>0.7506944444444444</v>
       </c>
-      <c r="I10" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="L10" s="5" t="s">
+      <c r="J10" s="1" t="s">
         <v>43</v>
+      </c>
+      <c r="M10" s="1" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="11">
       <c r="B11" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C11" s="1">
         <v>17.0</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E11" s="2">
         <v>40.676753</v>
@@ -782,35 +1228,2239 @@
       <c r="F11" s="2">
         <v>-74.324987</v>
       </c>
-      <c r="G11" s="6">
-        <v>373086.0</v>
-      </c>
-      <c r="H11" s="4">
+      <c r="G11" s="2"/>
+      <c r="H11" s="5">
+        <v>44368.0</v>
+      </c>
+      <c r="I11" s="4">
         <v>0.7020833333333333</v>
       </c>
-      <c r="I11" s="1" t="s">
+      <c r="J11" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K11" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="M11" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C12" s="1">
+        <v>14.0</v>
+      </c>
+      <c r="D12" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="J11" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="L11" s="5" t="s">
+      <c r="E12" s="2">
+        <v>40.64008</v>
+      </c>
+      <c r="F12" s="2">
+        <v>-74.447606</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="H12" s="5">
+        <v>44496.0</v>
+      </c>
+      <c r="I12" s="4">
+        <v>0.7020833333333333</v>
+      </c>
+      <c r="J12" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="K12" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="M12" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C13" s="1">
+        <v>16.0</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E13" s="2">
+        <v>40.639968</v>
+      </c>
+      <c r="F13" s="6">
+        <v>-74.447919</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="H13" s="5">
+        <v>44496.0</v>
+      </c>
+      <c r="I13" s="4">
+        <v>0.7416666666666667</v>
+      </c>
+      <c r="J13" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="K13" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="M13" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C14" s="1">
+        <v>15.0</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="E14" s="2">
+        <v>40.833896</v>
+      </c>
+      <c r="F14" s="2">
+        <v>-74.411892</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="H14" s="5">
+        <v>44500.0</v>
+      </c>
+      <c r="I14" s="4">
+        <v>0.7402777777777778</v>
+      </c>
+      <c r="J14" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K14" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="M14" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="E15" s="2">
+        <v>40.882944</v>
+      </c>
+      <c r="F15" s="2">
+        <v>-74.230284</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="H15" s="5">
+        <v>44640.0</v>
+      </c>
+      <c r="I15" s="4">
+        <v>0.7263888888888889</v>
+      </c>
+      <c r="J15" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K15" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="M15" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C16" s="1">
+        <v>18.0</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="E16" s="2">
+        <v>40.85009</v>
+      </c>
+      <c r="F16" s="2">
+        <v>-74.429599</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="H16" s="3">
+        <v>44517.0</v>
+      </c>
+      <c r="I16" s="4">
+        <v>0.63125</v>
+      </c>
+      <c r="J16" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K16" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="M16" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="E17" s="2">
+        <v>40.884441</v>
+      </c>
+      <c r="F17" s="2">
+        <v>-74.250901</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="H17" s="3">
+        <v>44532.0</v>
+      </c>
+      <c r="I17" s="4">
+        <v>0.5618055555555556</v>
+      </c>
+      <c r="J17" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K17" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="M17" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="E18" s="2">
+        <v>40.884378</v>
+      </c>
+      <c r="F18" s="2">
+        <v>-74.25085</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="H18" s="3">
+        <v>44535.0</v>
+      </c>
+      <c r="I18" s="4">
+        <v>0.5215277777777778</v>
+      </c>
+      <c r="J18" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K18" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="M18" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="E19" s="2">
+        <v>40.88442</v>
+      </c>
+      <c r="F19" s="2">
+        <v>-74.250918</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="H19" s="3">
+        <v>44535.0</v>
+      </c>
+      <c r="I19" s="4">
+        <v>0.6</v>
+      </c>
+      <c r="J19" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K19" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="M19" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C20" s="1">
+        <v>16.0</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E20" s="2">
+        <v>40.882958</v>
+      </c>
+      <c r="F20" s="2">
+        <v>-74.230273</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="H20" s="5">
+        <v>44640.0</v>
+      </c>
+      <c r="I20" s="4">
+        <v>0.6527777777777778</v>
+      </c>
+      <c r="J20" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="K20" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="M20" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="E21" s="2">
+        <v>40.882942</v>
+      </c>
+      <c r="F21" s="2">
+        <v>-74.230545</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="H21" s="5">
+        <v>44641.0</v>
+      </c>
+      <c r="I21" s="4">
+        <v>0.7006944444444444</v>
+      </c>
+      <c r="J21" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="K21" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="M21" s="1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C22" s="1">
+        <v>14.0</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="2">
+        <v>40.857196</v>
+      </c>
+      <c r="F22" s="2">
+        <v>-74.43023</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="H22" s="7">
+        <v>44661.0</v>
+      </c>
+      <c r="I22" s="4">
+        <v>0.6979166666666666</v>
+      </c>
+      <c r="J22" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="K22" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="M22" s="1" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C23" s="1">
+        <v>19.0</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="E23" s="2">
+        <v>40.639141</v>
+      </c>
+      <c r="F23" s="2">
+        <v>-74.449926</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="H23" s="7">
+        <v>44662.0</v>
+      </c>
+      <c r="I23" s="4">
+        <v>0.6979166666666666</v>
+      </c>
+      <c r="J23" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="K23" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="M23" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E24" s="2">
+        <v>40.731137</v>
+      </c>
+      <c r="F24" s="2">
+        <v>-74.307164</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="H24" s="3">
+        <v>44664.0</v>
+      </c>
+      <c r="I24" s="4">
+        <v>0.5951388888888889</v>
+      </c>
+      <c r="J24" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="K24" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="M24" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E25" s="2">
+        <v>40.884261</v>
+      </c>
+      <c r="F25" s="2">
+        <v>-74.125611</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="H25" s="5">
+        <v>44696.0</v>
+      </c>
+      <c r="I25" s="4">
+        <v>0.71875</v>
+      </c>
+      <c r="J25" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="K25" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="M25" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="G26" s="1"/>
+      <c r="H26" s="5">
+        <v>44702.0</v>
+      </c>
+      <c r="I26" s="4">
+        <v>0.7493055555555556</v>
+      </c>
+      <c r="J26" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="K26" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="M26" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="27" ht="15.0" customHeight="1">
+      <c r="B27" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="E27" s="2">
+        <v>40.855353</v>
+      </c>
+      <c r="F27" s="2">
+        <v>-74.109733</v>
+      </c>
+      <c r="G27" s="2"/>
+      <c r="H27" s="5">
+        <v>44702.0</v>
+      </c>
+      <c r="I27" s="4">
+        <v>0.8388888888888889</v>
+      </c>
+      <c r="J27" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="K27" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="M27" s="1" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="E28" s="2">
+        <v>41.042381</v>
+      </c>
+      <c r="F28" s="2">
+        <v>-73.987219</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="H28" s="5">
+        <v>44715.0</v>
+      </c>
+      <c r="I28" s="4">
+        <v>0.8166666666666667</v>
+      </c>
+      <c r="J28" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="K28" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="M28" s="1" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="H29" s="5">
+        <v>44719.0</v>
+      </c>
+      <c r="I29" s="4">
+        <v>0.6777777777777778</v>
+      </c>
+      <c r="J29" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="K29" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="M29" s="1" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="E30" s="2">
+        <v>40.854753</v>
+      </c>
+      <c r="F30" s="2">
+        <v>-74.109197</v>
+      </c>
+      <c r="G30" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="H30" s="5">
+        <v>44724.0</v>
+      </c>
+      <c r="I30" s="4">
+        <v>0.7576388888888889</v>
+      </c>
+      <c r="J30" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="K30" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="M30" s="1" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E31" s="2">
+        <v>40.639444</v>
+      </c>
+      <c r="F31" s="2">
+        <v>-74.450267</v>
+      </c>
+      <c r="G31" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="H31" s="5">
+        <v>44786.0</v>
+      </c>
+      <c r="I31" s="4">
+        <v>0.7354166666666667</v>
+      </c>
+      <c r="J31" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="K31" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="M31" s="1" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E32" s="2">
+        <v>40.684789</v>
+      </c>
+      <c r="F32" s="2">
+        <v>-74.296097</v>
+      </c>
+      <c r="G32" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="H32" s="7">
+        <v>44832.0</v>
+      </c>
+      <c r="I32" s="4">
+        <v>0.7069444444444445</v>
+      </c>
+      <c r="J32" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="K32" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="M32" s="1" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="E33" s="2">
+        <v>40.862872</v>
+      </c>
+      <c r="F33" s="2">
+        <v>-74.108353</v>
+      </c>
+      <c r="G33" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="H33" s="3">
+        <v>44915.0</v>
+      </c>
+      <c r="I33" s="4">
+        <v>0.8715277777777778</v>
+      </c>
+      <c r="J33" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="K33" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="M33" s="1" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="34" ht="15.0" customHeight="1">
+      <c r="B34" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="E34" s="2">
+        <v>40.860097</v>
+      </c>
+      <c r="F34" s="2">
+        <v>-74.120533</v>
+      </c>
+      <c r="G34" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="H34" s="3">
+        <v>44925.0</v>
+      </c>
+      <c r="I34" s="4">
+        <v>0.8715277777777778</v>
+      </c>
+      <c r="J34" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="K34" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="M34" s="1" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="E35" s="2">
+        <v>40.85483</v>
+      </c>
+      <c r="F35" s="2">
+        <v>-74.109764</v>
+      </c>
+      <c r="G35" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="H35" s="3">
+        <v>44929.0</v>
+      </c>
+      <c r="I35" s="4">
+        <v>0.725</v>
+      </c>
+      <c r="J35" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="K35" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="M35" s="1" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="E36" s="2">
+        <v>40.8633</v>
+      </c>
+      <c r="F36" s="2">
+        <v>-74.106678</v>
+      </c>
+      <c r="G36" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="H36" s="3">
+        <v>44930.0</v>
+      </c>
+      <c r="I36" s="4">
+        <v>0.6979166666666666</v>
+      </c>
+      <c r="J36" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="K36" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="M36" s="1" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="E37" s="2">
+        <v>40.85495</v>
+      </c>
+      <c r="F37" s="2">
+        <v>-74.109444</v>
+      </c>
+      <c r="G37" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="H37" s="3">
+        <v>44936.0</v>
+      </c>
+      <c r="I37" s="4">
+        <v>0.9173611111111111</v>
+      </c>
+      <c r="J37" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="K37" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="M37" s="1" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="E38" s="2">
+        <v>40.846383</v>
+      </c>
+      <c r="F38" s="2">
+        <v>-74.342022</v>
+      </c>
+      <c r="G38" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="H38" s="5">
+        <v>45005.0</v>
+      </c>
+      <c r="I38" s="4">
+        <v>0.775</v>
+      </c>
+      <c r="J38" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="K38" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="M38" s="1" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D39" s="1" t="s">
         <v>45</v>
       </c>
+      <c r="E39" s="2">
+        <v>40.846328</v>
+      </c>
+      <c r="F39" s="2">
+        <v>-74.341794</v>
+      </c>
+      <c r="G39" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="H39" s="5">
+        <v>45012.0</v>
+      </c>
+      <c r="I39" s="4">
+        <v>0.5763888888888888</v>
+      </c>
+      <c r="J39" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="K39" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="M39" s="1" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E40" s="2">
+        <v>40.846328</v>
+      </c>
+      <c r="F40" s="2">
+        <v>-74.341794</v>
+      </c>
+      <c r="G40" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="H40" s="5">
+        <v>45020.0</v>
+      </c>
+      <c r="I40" s="4">
+        <v>0.7208333333333333</v>
+      </c>
+      <c r="J40" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="K40" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="M40" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E41" s="2">
+        <v>40.846328</v>
+      </c>
+      <c r="F41" s="2">
+        <v>-74.341794</v>
+      </c>
+      <c r="G41" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="H41" s="5">
+        <v>45026.0</v>
+      </c>
+      <c r="I41" s="4">
+        <v>0.6944444444444444</v>
+      </c>
+      <c r="J41" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="K41" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="M41" s="1" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F42" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G42" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="H42" s="5">
+        <v>45039.0</v>
+      </c>
+      <c r="I42" s="4">
+        <v>0.6069444444444444</v>
+      </c>
+      <c r="J42" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="K42" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="M42" s="1" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F43" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G43" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="H43" s="5">
+        <v>45060.0</v>
+      </c>
+      <c r="I43" s="4">
+        <v>0.6277777777777778</v>
+      </c>
+      <c r="J43" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="K43" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="M43" s="1" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F44" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G44" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="H44" s="5">
+        <v>45067.0</v>
+      </c>
+      <c r="I44" s="4">
+        <v>0.5680555555555555</v>
+      </c>
+      <c r="J44" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="K44" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="M44" s="1" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F45" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G45" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="H45" s="5">
+        <v>45081.0</v>
+      </c>
+      <c r="I45" s="4">
+        <v>0.78125</v>
+      </c>
+      <c r="J45" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K45" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="M45" s="1" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F46" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G46" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="H46" s="5">
+        <v>45090.0</v>
+      </c>
+      <c r="I46" s="4">
+        <v>0.7472222222222222</v>
+      </c>
+      <c r="J46" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="K46" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="M46" s="1" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F47" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G47" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="H47" s="5">
+        <v>45096.0</v>
+      </c>
+      <c r="I47" s="4">
+        <v>0.7729166666666667</v>
+      </c>
+      <c r="J47" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K47" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="M47" s="1" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F48" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G48" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="H48" s="5">
+        <v>45111.0</v>
+      </c>
+      <c r="I48" s="4">
+        <v>0.63125</v>
+      </c>
+      <c r="J48" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K48" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="M48" s="1" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F49" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G49" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="H49" s="5">
+        <v>45111.0</v>
+      </c>
+      <c r="I49" s="4">
+        <v>0.7534722222222222</v>
+      </c>
+      <c r="J49" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K49" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="M49" s="1" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F50" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G50" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="H50" s="5">
+        <v>45111.0</v>
+      </c>
+      <c r="I50" s="4">
+        <v>0.7625</v>
+      </c>
+      <c r="J50" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K50" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="M50" s="1" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F51" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G51" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="H51" s="5">
+        <v>45126.0</v>
+      </c>
+      <c r="I51" s="4">
+        <v>0.6763888888888889</v>
+      </c>
+      <c r="J51" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="K51" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="M51" s="1" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="B52" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F52" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G52" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="H52" s="5">
+        <v>45142.0</v>
+      </c>
+      <c r="I52" s="4">
+        <v>0.7451388888888889</v>
+      </c>
+      <c r="J52" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="K52" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="M52" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F53" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G53" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="H53" s="5">
+        <v>45144.0</v>
+      </c>
+      <c r="I53" s="4">
+        <v>0.6270833333333333</v>
+      </c>
+      <c r="J53" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="K53" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="M53" s="1" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F54" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G54" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="H54" s="5">
+        <v>45144.0</v>
+      </c>
+      <c r="I54" s="4">
+        <v>0.6270833333333333</v>
+      </c>
+      <c r="J54" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="K54" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="M54" s="1" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E55" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F55" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G55" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="H55" s="5">
+        <v>45146.0</v>
+      </c>
+      <c r="I55" s="4">
+        <v>0.6569444444444444</v>
+      </c>
+      <c r="J55" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="K55" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="M55" s="1" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="B56" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E56" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F56" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G56" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="H56" s="5">
+        <v>45146.0</v>
+      </c>
+      <c r="I56" s="4">
+        <v>0.6569444444444444</v>
+      </c>
+      <c r="J56" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="K56" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="M56" s="1" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="B57" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="E57" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F57" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G57" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="H57" s="5">
+        <v>45146.0</v>
+      </c>
+      <c r="I57" s="4">
+        <v>0.6798611111111111</v>
+      </c>
+      <c r="J57" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="K57" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="M57" s="1" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="B58" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F58" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G58" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="H58" s="5">
+        <v>45151.0</v>
+      </c>
+      <c r="I58" s="4">
+        <v>0.6555555555555556</v>
+      </c>
+      <c r="J58" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="K58" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="M58" s="1" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="B59" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E59" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F59" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G59" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="H59" s="5">
+        <v>45152.0</v>
+      </c>
+      <c r="I59" s="4">
+        <v>0.7465277777777778</v>
+      </c>
+      <c r="J59" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="K59" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="M59" s="1" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="B60" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="E60" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F60" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G60" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="H60" s="5">
+        <v>45275.0</v>
+      </c>
+      <c r="I60" s="4">
+        <v>0.5201388888888889</v>
+      </c>
+      <c r="J60" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K60" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="M60" s="1" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="B61" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="E61" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F61" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G61" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="H61" s="5">
+        <v>45286.0</v>
+      </c>
+      <c r="I61" s="4">
+        <v>0.6993055555555555</v>
+      </c>
+      <c r="J61" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="K61" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="M61" s="1" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="B62" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="E62" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F62" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G62" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="H62" s="5">
+        <v>45321.0</v>
+      </c>
+      <c r="I62" s="4">
+        <v>0.6534722222222222</v>
+      </c>
+      <c r="J62" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K62" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="M62" s="1" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="B63" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E63" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F63" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G63" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="H63" s="5">
+        <v>45363.0</v>
+      </c>
+      <c r="I63" s="4">
+        <v>0.6423611111111112</v>
+      </c>
+      <c r="J63" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="K63" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="M63" s="1" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="B64" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E64" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F64" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G64" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="H64" s="5">
+        <v>45368.0</v>
+      </c>
+      <c r="I64" s="4">
+        <v>0.5604166666666667</v>
+      </c>
+      <c r="J64" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K64" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="M64" s="1" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="B65" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E65" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F65" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G65" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="H65" s="5">
+        <v>45368.0</v>
+      </c>
+      <c r="I65" s="4">
+        <v>0.6284722222222222</v>
+      </c>
+      <c r="J65" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K65" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="M65" s="1" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="B66" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E66" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F66" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G66" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="H66" s="5">
+        <v>45383.0</v>
+      </c>
+      <c r="I66" s="4">
+        <v>0.6284722222222222</v>
+      </c>
+      <c r="J66" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="K66" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="M66" s="1" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="B67" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E67" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F67" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G67" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="H67" s="8">
+        <v>45391.0</v>
+      </c>
+      <c r="I67" s="4">
+        <v>0.60625</v>
+      </c>
+      <c r="J67" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="K67" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="M67" s="1" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="B68" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="E68" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F68" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G68" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="H68" s="8">
+        <v>45438.0</v>
+      </c>
+      <c r="I68" s="4">
+        <v>0.6555555555555556</v>
+      </c>
+      <c r="J68" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="K68" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="M68" s="1" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="B69" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="E69" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F69" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G69" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="H69" s="8">
+        <v>45438.0</v>
+      </c>
+      <c r="I69" s="4">
+        <v>0.5930555555555556</v>
+      </c>
+      <c r="J69" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="K69" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="M69" s="1" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="B70" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="E70" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F70" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G70" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="H70" s="8">
+        <v>45439.0</v>
+      </c>
+      <c r="I70" s="4">
+        <v>0.7173611111111111</v>
+      </c>
+      <c r="J70" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="K70" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="M70" s="1" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="B71" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="E71" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F71" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G71" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="H71" s="8">
+        <v>45443.0</v>
+      </c>
+      <c r="I71" s="4">
+        <v>0.6201388888888889</v>
+      </c>
+      <c r="J71" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K71" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="M71" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="B72" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="E72" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F72" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G72" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="H72" s="8">
+        <v>45448.0</v>
+      </c>
+      <c r="I72" s="4">
+        <v>0.6201388888888889</v>
+      </c>
+      <c r="J72" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="K72" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="M72" s="1" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="B73" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="E73" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F73" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G73" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="H73" s="8">
+        <v>45448.0</v>
+      </c>
+      <c r="I73" s="4">
+        <v>0.6763888888888889</v>
+      </c>
+      <c r="J73" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K73" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="M73" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="B74" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="E74" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F74" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G74" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="H74" s="8">
+        <v>45457.0</v>
+      </c>
+      <c r="I74" s="4">
+        <v>0.7229166666666667</v>
+      </c>
+      <c r="J74" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="K74" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="M74" s="1" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="B75" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="E75" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F75" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G75" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="H75" s="8">
+        <v>45461.0</v>
+      </c>
+      <c r="I75" s="4">
+        <v>0.7659722222222223</v>
+      </c>
+      <c r="J75" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="K75" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="M75" s="1" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="B76" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="E76" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F76" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G76" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="H76" s="8">
+        <v>45466.0</v>
+      </c>
+      <c r="I76" s="4">
+        <v>0.8340277777777778</v>
+      </c>
+      <c r="J76" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="K76" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="M76" s="1" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="B77" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="E77" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F77" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G77" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="H77" s="8">
+        <v>45475.0</v>
+      </c>
+      <c r="I77" s="4">
+        <v>0.6923611111111111</v>
+      </c>
+      <c r="J77" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="K77" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="M77" s="1" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="B78" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E78" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F78" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G78" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="H78" s="8">
+        <v>45475.0</v>
+      </c>
+      <c r="I78" s="4">
+        <v>0.7159722222222222</v>
+      </c>
+      <c r="J78" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="K78" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="M78" s="1" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="B79" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="E79" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F79" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G79" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="H79" s="8">
+        <v>45477.0</v>
+      </c>
+      <c r="I79" s="4">
+        <v>0.6888888888888889</v>
+      </c>
+      <c r="J79" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="K79" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="M79" s="1" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="9"/>
+      <c r="B80" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="C80" s="9"/>
+      <c r="D80" s="9"/>
+      <c r="E80" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="F80" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="G80" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="H80" s="11">
+        <v>45480.0</v>
+      </c>
+      <c r="I80" s="12">
+        <v>0.6895833333333333</v>
+      </c>
+      <c r="J80" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="K80" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="L80" s="9"/>
+      <c r="M80" s="13" t="s">
+        <v>174</v>
+      </c>
+      <c r="N80" s="9"/>
+      <c r="O80" s="9"/>
+      <c r="P80" s="9"/>
+      <c r="Q80" s="9"/>
+      <c r="R80" s="9"/>
+      <c r="S80" s="9"/>
+      <c r="T80" s="9"/>
+      <c r="U80" s="9"/>
+      <c r="V80" s="9"/>
+      <c r="W80" s="9"/>
+      <c r="X80" s="9"/>
+      <c r="Y80" s="9"/>
+      <c r="Z80" s="9"/>
+      <c r="AA80" s="9"/>
+      <c r="AB80" s="9"/>
+    </row>
+    <row r="81">
+      <c r="B81" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="E81" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F81" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G81" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="H81" s="8">
+        <v>45487.0</v>
+      </c>
+      <c r="I81" s="4">
+        <v>0.8548611111111111</v>
+      </c>
+      <c r="J81" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="K81" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="M81" s="1" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="B82" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E82" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F82" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G82" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="H82" s="8">
+        <v>45489.0</v>
+      </c>
+      <c r="I82" s="4">
+        <v>0.7159722222222222</v>
+      </c>
+      <c r="J82" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="K82" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="M82" s="1" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="B83" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E83" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F83" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G83" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="H83" s="8">
+        <v>45544.0</v>
+      </c>
+      <c r="I83" s="4">
+        <v>0.7048611111111112</v>
+      </c>
+      <c r="J83" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="K83" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="M83" s="1" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="B84" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E84" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F84" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G84" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="H84" s="8">
+        <v>45564.0</v>
+      </c>
+      <c r="I84" s="4">
+        <v>0.6541666666666667</v>
+      </c>
+      <c r="J84" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="K84" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="M84" s="1" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="B85" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="E85" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F85" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G85" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="H85" s="8">
+        <v>45614.0</v>
+      </c>
+      <c r="I85" s="4">
+        <v>0.8548611111111111</v>
+      </c>
+      <c r="J85" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="K85" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="M85" s="1" t="s">
+        <v>180</v>
+      </c>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink r:id="rId1" ref="L2"/>
-    <hyperlink r:id="rId2" ref="L3"/>
-    <hyperlink r:id="rId3" ref="L4"/>
-    <hyperlink r:id="rId4" ref="L5"/>
-    <hyperlink r:id="rId5" ref="L6"/>
-    <hyperlink r:id="rId6" ref="L7"/>
-    <hyperlink r:id="rId7" ref="L8"/>
-    <hyperlink r:id="rId8" ref="L9"/>
-    <hyperlink r:id="rId9" ref="L10"/>
-    <hyperlink r:id="rId10" ref="L11"/>
-  </hyperlinks>
-  <drawing r:id="rId11"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/data/catches.xlsx
+++ b/data/catches.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="536" uniqueCount="181">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="536" uniqueCount="180">
   <si>
     <t>id</t>
   </si>
@@ -379,7 +379,7 @@
     <t>Warm</t>
   </si>
   <si>
-    <t>PXL_20230404_211818350.jpg</t>
+    <t>PXL_20230804_215325097.jpg</t>
   </si>
   <si>
     <t>PXL_20230410_204036629.jpg</t>
@@ -431,9 +431,6 @@
   </si>
   <si>
     <t>PXL_20230704_221848501.jpg</t>
-  </si>
-  <si>
-    <t>PXL_20230804_215325097.jpg</t>
   </si>
   <si>
     <t>PXL_20230806_190306695.jpg</t>
@@ -2481,7 +2478,7 @@
         <v>125</v>
       </c>
       <c r="M52" s="1" t="s">
-        <v>140</v>
+        <v>122</v>
       </c>
     </row>
     <row r="53">
@@ -2510,7 +2507,7 @@
         <v>128</v>
       </c>
       <c r="M53" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="54">
@@ -2539,7 +2536,7 @@
         <v>128</v>
       </c>
       <c r="M54" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="55">
@@ -2568,7 +2565,7 @@
         <v>125</v>
       </c>
       <c r="M55" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="56">
@@ -2597,12 +2594,12 @@
         <v>125</v>
       </c>
       <c r="M56" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="57">
       <c r="B57" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E57" s="2" t="s">
         <v>25</v>
@@ -2626,12 +2623,12 @@
         <v>125</v>
       </c>
       <c r="M57" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="58">
       <c r="B58" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E58" s="2" t="s">
         <v>25</v>
@@ -2655,7 +2652,7 @@
         <v>128</v>
       </c>
       <c r="M58" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="59">
@@ -2684,7 +2681,7 @@
         <v>125</v>
       </c>
       <c r="M59" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="60">
@@ -2698,7 +2695,7 @@
         <v>25</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="H60" s="5">
         <v>45275.0</v>
@@ -2713,7 +2710,7 @@
         <v>128</v>
       </c>
       <c r="M60" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="61">
@@ -2742,7 +2739,7 @@
         <v>125</v>
       </c>
       <c r="M61" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="62">
@@ -2756,7 +2753,7 @@
         <v>25</v>
       </c>
       <c r="G62" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="H62" s="5">
         <v>45321.0</v>
@@ -2771,7 +2768,7 @@
         <v>125</v>
       </c>
       <c r="M62" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="63">
@@ -2785,7 +2782,7 @@
         <v>25</v>
       </c>
       <c r="G63" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="H63" s="5">
         <v>45363.0</v>
@@ -2800,7 +2797,7 @@
         <v>128</v>
       </c>
       <c r="M63" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="64">
@@ -2814,7 +2811,7 @@
         <v>25</v>
       </c>
       <c r="G64" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="H64" s="5">
         <v>45368.0</v>
@@ -2829,7 +2826,7 @@
         <v>128</v>
       </c>
       <c r="M64" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="65">
@@ -2858,7 +2855,7 @@
         <v>128</v>
       </c>
       <c r="M65" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="66">
@@ -2872,7 +2869,7 @@
         <v>25</v>
       </c>
       <c r="G66" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="H66" s="5">
         <v>45383.0</v>
@@ -2881,13 +2878,13 @@
         <v>0.6284722222222222</v>
       </c>
       <c r="J66" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="K66" s="1" t="s">
         <v>125</v>
       </c>
       <c r="M66" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="67">
@@ -2916,7 +2913,7 @@
         <v>128</v>
       </c>
       <c r="M67" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="68">
@@ -2939,13 +2936,13 @@
         <v>0.6555555555555556</v>
       </c>
       <c r="J68" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="K68" s="1" t="s">
         <v>128</v>
       </c>
       <c r="M68" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="69">
@@ -2968,13 +2965,13 @@
         <v>0.5930555555555556</v>
       </c>
       <c r="J69" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="K69" s="1" t="s">
         <v>125</v>
       </c>
       <c r="M69" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="70">
@@ -3003,12 +3000,12 @@
         <v>125</v>
       </c>
       <c r="M70" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="71">
       <c r="B71" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E71" s="2" t="s">
         <v>25</v>
@@ -3032,12 +3029,12 @@
         <v>128</v>
       </c>
       <c r="M71" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="72">
       <c r="B72" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E72" s="2" t="s">
         <v>25</v>
@@ -3061,12 +3058,12 @@
         <v>128</v>
       </c>
       <c r="M72" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="73">
       <c r="B73" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E73" s="2" t="s">
         <v>25</v>
@@ -3090,7 +3087,7 @@
         <v>128</v>
       </c>
       <c r="M73" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="74">
@@ -3113,13 +3110,13 @@
         <v>0.7229166666666667</v>
       </c>
       <c r="J74" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="K74" s="1" t="s">
         <v>125</v>
       </c>
       <c r="M74" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="75">
@@ -3142,18 +3139,18 @@
         <v>0.7659722222222223</v>
       </c>
       <c r="J75" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="K75" s="1" t="s">
         <v>125</v>
       </c>
       <c r="M75" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="76">
       <c r="B76" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E76" s="2" t="s">
         <v>25</v>
@@ -3177,7 +3174,7 @@
         <v>128</v>
       </c>
       <c r="M76" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="77">
@@ -3200,13 +3197,13 @@
         <v>0.6923611111111111</v>
       </c>
       <c r="J77" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="K77" s="1" t="s">
         <v>128</v>
       </c>
       <c r="M77" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="78">
@@ -3229,13 +3226,13 @@
         <v>0.7159722222222222</v>
       </c>
       <c r="J78" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="K78" s="1" t="s">
         <v>128</v>
       </c>
       <c r="M78" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="79">
@@ -3258,13 +3255,13 @@
         <v>0.6888888888888889</v>
       </c>
       <c r="J79" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="K79" s="1" t="s">
         <v>128</v>
       </c>
       <c r="M79" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="80">
@@ -3290,14 +3287,14 @@
         <v>0.6895833333333333</v>
       </c>
       <c r="J80" s="9" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="K80" s="9" t="s">
         <v>128</v>
       </c>
       <c r="L80" s="9"/>
       <c r="M80" s="13" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="N80" s="9"/>
       <c r="O80" s="9"/>
@@ -3317,7 +3314,7 @@
     </row>
     <row r="81">
       <c r="B81" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E81" s="2" t="s">
         <v>25</v>
@@ -3341,7 +3338,7 @@
         <v>128</v>
       </c>
       <c r="M81" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="82">
@@ -3355,7 +3352,7 @@
         <v>25</v>
       </c>
       <c r="G82" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H82" s="8">
         <v>45489.0</v>
@@ -3370,7 +3367,7 @@
         <v>125</v>
       </c>
       <c r="M82" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="83">
@@ -3399,7 +3396,7 @@
         <v>125</v>
       </c>
       <c r="M83" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="84">
@@ -3428,12 +3425,12 @@
         <v>125</v>
       </c>
       <c r="M84" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="85">
       <c r="B85" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E85" s="2" t="s">
         <v>25</v>
@@ -3457,7 +3454,7 @@
         <v>128</v>
       </c>
       <c r="M85" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
   </sheetData>
